--- a/claude-with-tools/plots/python_tool_types.xlsx
+++ b/claude-with-tools/plots/python_tool_types.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emmayu/Desktop/llm-with-tools/claude-with-tools/plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{847555B2-C45A-4B4A-B877-F217C8F56399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BD6EAF-BA4A-E742-B6B7-BE8852C69BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{571C3249-75F5-A44D-9137-269BD9E4E7AD}"/>
+    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="2" xr2:uid="{571C3249-75F5-A44D-9137-269BD9E4E7AD}"/>
   </bookViews>
   <sheets>
     <sheet name="sample 1 - python" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
   <si>
     <t>model name</t>
   </si>
@@ -60,9 +60,6 @@
     <t>read</t>
   </si>
   <si>
-    <t>git show</t>
-  </si>
-  <si>
     <t>ls</t>
   </si>
   <si>
@@ -72,16 +69,16 @@
     <t>cat</t>
   </si>
   <si>
-    <t>python3 -c</t>
-  </si>
-  <si>
-    <t>python -m pytest</t>
-  </si>
-  <si>
-    <t>git log</t>
-  </si>
-  <si>
     <t>pwd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">git </t>
+  </si>
+  <si>
+    <t>python</t>
+  </si>
+  <si>
+    <t>git</t>
   </si>
 </sst>
 </file>
@@ -461,10 +458,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD337267-8273-9446-ABF5-CFEB65B3234C}">
-  <dimension ref="A3:L5"/>
+  <dimension ref="A3:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -478,31 +475,25 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="29">
+    </row>
+    <row r="4" spans="1:10" ht="29">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -533,14 +524,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="29">
+    </row>
+    <row r="5" spans="1:10" ht="29">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -569,12 +554,6 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
         <v>0</v>
       </c>
     </row>
@@ -585,10 +564,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687A6908-63F5-7549-BD00-4919F6491F7A}">
-  <dimension ref="A3:L5"/>
+  <dimension ref="A3:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -602,31 +581,25 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="29">
+    </row>
+    <row r="4" spans="1:10" ht="29">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -657,14 +630,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="29">
+    </row>
+    <row r="5" spans="1:10" ht="29">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -693,12 +660,6 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
         <v>0</v>
       </c>
     </row>
@@ -709,13 +670,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211C13F9-17C6-DA4B-B430-0BB2FA7473E8}">
-  <dimension ref="A3:L5"/>
+  <dimension ref="A3:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -729,31 +687,25 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="29">
+    </row>
+    <row r="4" spans="1:10" ht="29">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -767,31 +719,25 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -811,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -820,12 +766,6 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
         <v>0</v>
       </c>
     </row>
@@ -836,10 +776,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A8CE86-68B3-0547-986E-86C757DB6415}">
-  <dimension ref="A3:L5"/>
+  <dimension ref="A3:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -853,31 +793,25 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="29">
+    </row>
+    <row r="4" spans="1:10" ht="29">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -908,14 +842,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="29">
+    </row>
+    <row r="5" spans="1:10" ht="29">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -944,12 +872,6 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
         <v>0</v>
       </c>
     </row>
@@ -960,10 +882,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217C092B-E717-BC4A-A065-BC1FE55E7A1C}">
-  <dimension ref="A3:L5"/>
+  <dimension ref="A3:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -977,31 +899,25 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="29">
+    </row>
+    <row r="4" spans="1:10" ht="29">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1021,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1030,16 +946,10 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="29">
+    <row r="5" spans="1:10" ht="29">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1068,12 +978,6 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
         <v>0</v>
       </c>
     </row>
